--- a/results/Int Task Remove ACC 0.2/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_9_permute.xlsx
@@ -440,307 +440,307 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6899599707674562</v>
+        <v>0.6739279066391997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.662112662427778</v>
+        <v>0.6627117004020748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6601213863559393</v>
+        <v>0.6715954144629793</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6500395963464413</v>
+        <v>0.6830567106258261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6645049947417071</v>
+        <v>0.6828969247261996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6640039927376991</v>
+        <v>0.6837989829722978</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6661423227649709</v>
+        <v>0.6912649950472738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6564526766366278</v>
+        <v>0.6857539730031855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6566360166330119</v>
+        <v>0.6641128508605521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6506112606407224</v>
+        <v>0.661106838836504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6442834843766313</v>
+        <v>0.6361458622454566</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6473385143858237</v>
+        <v>0.6381498702614887</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6440874124360538</v>
+        <v>0.6421941723345038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6421324224051661</v>
+        <v>0.6468012263408647</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6451384344292141</v>
+        <v>0.6478522483340251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6292807979364066</v>
+        <v>0.649709202394624</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6417931160924135</v>
+        <v>0.649709202394624</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6167920338771571</v>
+        <v>0.6518004242283806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6354506980925001</v>
+        <v>0.6413646861703076</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6327349743960602</v>
+        <v>0.6379919941534913</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6200902440204424</v>
+        <v>0.6235425106884671</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6173636981714381</v>
+        <v>0.6206708206756588</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6178647001754461</v>
+        <v>0.6239855823463955</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6334339581322748</v>
+        <v>0.6239855823463955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6219363759284771</v>
+        <v>0.6239855823463955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6219363759284771</v>
+        <v>0.6246209063616432</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.624258045952133</v>
+        <v>0.6363126507143894</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6095348256869521</v>
+        <v>0.5229467830196607</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.571642013378727</v>
+        <v>0.5216271170040208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5935027615586955</v>
+        <v>0.5216271170040208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5841199552854121</v>
+        <v>0.5311442452885441</v>
       </c>
     </row>
     <row r="33">
@@ -750,77 +750,77 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5841199552854121</v>
+        <v>0.5311442452885441</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.542905378737144</v>
+        <v>0.5274901773050549</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5538402090075959</v>
+        <v>0.5289677194286923</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5515312709281333</v>
+        <v>0.5248253813853884</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4808065941285367</v>
+        <v>0.5205487213308447</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4811242561361605</v>
+        <v>0.5314708196571033</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.475212177849982</v>
+        <v>0.529675615525842</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.475212177849982</v>
+        <v>0.5366005199726008</v>
       </c>
     </row>
     <row r="41">
@@ -830,497 +830,497 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4712404478588689</v>
+        <v>0.538214293899107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4643371877172388</v>
+        <v>0.5465715420676168</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4689442417235997</v>
+        <v>0.5469273999078207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4689442417235997</v>
+        <v>0.5464263979038128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4789789235395824</v>
+        <v>0.5522315278587671</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4835732456017499</v>
+        <v>0.5426144538123261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5103765345175739</v>
+        <v>0.5464665035280217</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5055823209315708</v>
+        <v>0.5156042708033602</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.51191391677892</v>
+        <v>0.5366278936526165</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5091657266247871</v>
+        <v>0.5244548818093621</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5211662206242218</v>
+        <v>0.4938300998439064</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5066715387573113</v>
+        <v>0.4935124378362825</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.497693608309376</v>
+        <v>0.4970067199201452</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5024222523827834</v>
+        <v>0.4966890579125213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4990368284217737</v>
+        <v>0.4971900599165294</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5085940623305061</v>
+        <v>0.4970557379052896</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5062469284184634</v>
+        <v>0.4959684298711782</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5070655924300953</v>
+        <v>0.4975204538683466</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5109010906183395</v>
+        <v>0.4975077219241533</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.511491216231701</v>
+        <v>0.4974224178980579</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5072272881213507</v>
+        <v>0.4979851698314036</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5034783671536212</v>
+        <v>0.4774606391945262</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4960104452870162</v>
+        <v>0.4541732766676937</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.503937353741791</v>
+        <v>0.4504033479920451</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5030696717450148</v>
+        <v>0.4519279983091978</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4994283357057189</v>
+        <v>0.4673081868947552</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5039246217975978</v>
+        <v>0.4702524489894656</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4955310875881369</v>
+        <v>0.4673934909208506</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4999146959739046</v>
+        <v>0.4673934909208506</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4999146959739046</v>
+        <v>0.4568635364757469</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4999146959739046</v>
+        <v>0.4548015981136351</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4997313559775205</v>
+        <v>0.4498896140438437</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5000490179851443</v>
+        <v>0.4706681469673782</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4990960319622727</v>
+        <v>0.4805487722586214</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4994136939698966</v>
+        <v>0.4689786179729217</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5000980359702887</v>
+        <v>0.470345392182077</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5016990779526015</v>
+        <v>0.4633676501669158</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5023471339120427</v>
+        <v>0.4615106961063168</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5055492178766682</v>
+        <v>0.4575733423645257</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5052315558690443</v>
+        <v>0.4621186464415489</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5045472138686522</v>
+        <v>0.4621186464415489</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4996823379923761</v>
+        <v>0.4704739848184297</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4996823379923761</v>
+        <v>0.4715014527148325</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4996823379923761</v>
+        <v>0.4715014527148325</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4996823379923761</v>
+        <v>0.4983652183655749</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5016666114949085</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5041569797791262</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5095591437003614</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5063678818883002</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5027991179309063</v>
       </c>
     </row>
   </sheetData>
